--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -776,7 +803,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -806,6 +833,75 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920117</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920152</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,33 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -504,19 +477,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -530,19 +503,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -556,10 +529,10 @@
         <v>19</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>16</v>
@@ -568,7 +541,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -621,16 +594,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -644,16 +620,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -667,16 +646,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
         <v>16</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -729,19 +711,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,19 +737,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>93.33</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,10 +763,10 @@
         <v>19</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>16</v>
@@ -793,7 +775,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -833,75 +815,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920117</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920130</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920152</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
@@ -646,7 +646,7 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -658,7 +658,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20221.xlsx
@@ -723,7 +723,7 @@
         <v>92.86</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,16 +766,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
